--- a/Policy-Document-Generation/Policy-Document-Generation/wwwroot/Data/Data.xlsx
+++ b/Policy-Document-Generation/Policy-Document-Generation/wwwroot/Data/Data.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blog\Insurance\Policy-Document-Generation\Policy-Document-Generation\wwwroot\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blog\Insurance-Usecase\Policy-Document-Generation\Policy-Document-Generation\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE83C25A-05A6-4230-AE6A-9AFB9EC785E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C43B51-3834-45B5-9AD8-B45763862C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PolicyDetails" sheetId="1" r:id="rId1"/>
     <sheet name="Endorsements" sheetId="2" r:id="rId2"/>
-    <sheet name="ClaimLetter" sheetId="3" r:id="rId3"/>
-    <sheet name="aaa" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
   <si>
     <t>PolicyNumber</t>
   </si>
@@ -131,9 +129,6 @@
     <t>IssueDate</t>
   </si>
   <si>
-    <t>US-POL-1001</t>
-  </si>
-  <si>
     <t>Individual</t>
   </si>
   <si>
@@ -173,9 +168,6 @@
     <t>Authorized Officer</t>
   </si>
   <si>
-    <t>UK-POL-2001</t>
-  </si>
-  <si>
     <t>Family</t>
   </si>
   <si>
@@ -218,9 +210,6 @@
     <t>Regional Director</t>
   </si>
   <si>
-    <t>AU-POL-3001</t>
-  </si>
-  <si>
     <t>Liam</t>
   </si>
   <si>
@@ -371,230 +360,20 @@
     <t>michael.brown@company.au</t>
   </si>
   <si>
-    <t>ClaimDate</t>
-  </si>
-  <si>
-    <t>DateOfLoss</t>
-  </si>
-  <si>
-    <t>ClaimType</t>
-  </si>
-  <si>
-    <t>ClaimAmount</t>
-  </si>
-  <si>
-    <t>ClaimStatus</t>
-  </si>
-  <si>
-    <t>NextSteps</t>
-  </si>
-  <si>
-    <t>AdjusterName</t>
-  </si>
-  <si>
-    <t>AdjusterPhone</t>
-  </si>
-  <si>
-    <t>AdjusterEmail</t>
-  </si>
-  <si>
-    <t>94105</t>
-  </si>
-  <si>
-    <t>05-Jan-2026</t>
-  </si>
-  <si>
-    <t>03-Jan-2026</t>
-  </si>
-  <si>
-    <t>Accidental Damage</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>Under Review</t>
-  </si>
-  <si>
-    <t>Provide repair estimates and photographs</t>
-  </si>
-  <si>
-    <t>Laura Simmons</t>
-  </si>
-  <si>
-    <t>+1-415-555-7744</t>
-  </si>
-  <si>
-    <t>laura.simmons@insurance.com</t>
-  </si>
-  <si>
-    <t>15-Mar-2026</t>
-  </si>
-  <si>
-    <t>12-Mar-2026</t>
-  </si>
-  <si>
-    <t>Medical Reimbursement</t>
-  </si>
-  <si>
-    <t>4800</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Settlement will be credited to your account</t>
-  </si>
-  <si>
-    <t>Daniel Wright</t>
-  </si>
-  <si>
-    <t>+44-20-7946-5521</t>
-  </si>
-  <si>
-    <t>daniel.wright@insurance.co.uk</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>28-Mar-2026</t>
-  </si>
-  <si>
-    <t>27-Mar-2026</t>
-  </si>
-  <si>
-    <t>Hospitalization</t>
-  </si>
-  <si>
-    <t>8200</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Medical reports verification in progress</t>
-  </si>
-  <si>
-    <t>Emily Harper</t>
-  </si>
-  <si>
-    <t>+61-2-9374-8899</t>
-  </si>
-  <si>
-    <t>emily.harper@insurance.au</t>
-  </si>
-  <si>
-    <t>ClaimLetterID</t>
-  </si>
-  <si>
-    <t>ClaimNumber</t>
-  </si>
-  <si>
-    <t>InsuredAddress</t>
-  </si>
-  <si>
-    <t>CL-001</t>
-  </si>
-  <si>
-    <t>10-Jan-2026</t>
-  </si>
-  <si>
-    <t>CLM-US-90001</t>
-  </si>
-  <si>
-    <t>742 Evergreen Terrace</t>
-  </si>
-  <si>
-    <t>CL-002</t>
-  </si>
-  <si>
-    <t>22-Mar-2026</t>
-  </si>
-  <si>
-    <t>CLM-UK-78211</t>
-  </si>
-  <si>
-    <t>CL-003</t>
-  </si>
-  <si>
-    <t>04-Apr-2026</t>
-  </si>
-  <si>
-    <t>CLM-AU-55421</t>
-  </si>
-  <si>
-    <t>CoverageChanges</t>
-  </si>
-  <si>
-    <t>PreviousPremium</t>
-  </si>
-  <si>
-    <t>PremiumAdjustment</t>
-  </si>
-  <si>
-    <t>NewPremium</t>
-  </si>
-  <si>
-    <t>END-US-1001</t>
-  </si>
-  <si>
-    <t>15-Feb-2026</t>
-  </si>
-  <si>
-    <t>742 Evergreen Terrace, San Francisco, CA 94105</t>
-  </si>
-  <si>
-    <t>Coverage Enhancement</t>
-  </si>
-  <si>
-    <t>Critical Illness coverage added to the base policy</t>
-  </si>
-  <si>
-    <t>Critical Illness Rider added with higher sum assured</t>
-  </si>
-  <si>
-    <t>END-UK-2001</t>
-  </si>
-  <si>
-    <t>10-Jun-2026</t>
-  </si>
-  <si>
-    <t>02-Jun-2026</t>
-  </si>
-  <si>
-    <t>18 Baker Street, London, NW1 6XE</t>
-  </si>
-  <si>
-    <t>Hospital cash benefit limit increased</t>
-  </si>
-  <si>
-    <t>Hospital Cash daily limit increased</t>
-  </si>
-  <si>
-    <t>END-AU-3001</t>
-  </si>
-  <si>
-    <t>20-Apr-2026</t>
-  </si>
-  <si>
-    <t>12-Apr-2026</t>
-  </si>
-  <si>
-    <t>55 Harbour Road, Sydney, NSW 2000</t>
-  </si>
-  <si>
-    <t>Premium revised due to risk reassessment</t>
-  </si>
-  <si>
-    <t>No change in coverage benefits</t>
+    <t>POL001</t>
+  </si>
+  <si>
+    <t>POL002</t>
+  </si>
+  <si>
+    <t>POL003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,11 +394,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -658,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -677,9 +451,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1020,13 +791,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -1035,7 +806,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>8</v>
@@ -1065,7 +836,7 @@
         <v>16</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>17</v>
@@ -1112,10 +883,10 @@
     </row>
     <row r="2" spans="1:36" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C2" s="4">
         <v>46023</v>
@@ -1124,50 +895,50 @@
         <v>49674</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H2" s="5">
         <v>36842</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J2" s="3">
         <f>1-415-555-9821</f>
         <v>-10790</v>
       </c>
       <c r="K2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="O2" s="3">
         <v>94105</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="T2" s="3">
         <v>1000000</v>
@@ -1209,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="AG2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="AJ2" s="4">
         <v>46037</v>
@@ -1223,10 +994,10 @@
     </row>
     <row r="3" spans="1:36" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4">
         <v>46096</v>
@@ -1235,50 +1006,50 @@
         <v>51574</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H3" s="5">
         <v>37174</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J3" s="3">
         <f>44-20-7946-958</f>
         <v>-8880</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="T3" s="3">
         <v>750000</v>
@@ -1320,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AJ3" s="4">
         <v>46101</v>
@@ -1331,10 +1102,10 @@
     </row>
     <row r="4" spans="1:36" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4">
         <v>46113</v>
@@ -1343,50 +1114,50 @@
         <v>49765</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3">
         <f>61-2-9374-4000</f>
         <v>-13315</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O4" s="3">
         <v>2000</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="T4" s="3">
         <v>600000</v>
@@ -1428,13 +1199,13 @@
         <v>1</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AJ4" s="4">
         <v>46117</v>
@@ -1465,625 +1236,105 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
         <v>83</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
         <v>88</v>
       </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
         <v>93</v>
       </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>94</v>
-      </c>
-      <c r="D5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C59AA0-8D7E-417F-A657-02C3D49773E6}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="15.77734375" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" customWidth="1"/>
-    <col min="16" max="16" width="11.109375" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" customWidth="1"/>
-    <col min="18" max="18" width="16.109375" customWidth="1"/>
-    <col min="19" max="19" width="14.109375" customWidth="1"/>
-    <col min="20" max="20" width="15.88671875" customWidth="1"/>
-    <col min="21" max="21" width="10.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89202751-5CCB-40AC-91EE-BA92D664994F}">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="18.21875" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.21875" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" customWidth="1"/>
-    <col min="14" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="13.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M2" s="3">
-        <v>150</v>
-      </c>
-      <c r="N2" s="3">
-        <v>1350</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L3" s="3">
-        <v>980</v>
-      </c>
-      <c r="M3" s="3">
-        <v>120</v>
-      </c>
-      <c r="N3" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="L4" s="3">
-        <v>760</v>
-      </c>
-      <c r="M4" s="3">
-        <v>-40</v>
-      </c>
-      <c r="N4" s="3">
-        <v>720</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Policy-Document-Generation/Policy-Document-Generation/wwwroot/Data/Data.xlsx
+++ b/Policy-Document-Generation/Policy-Document-Generation/wwwroot/Data/Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blog\Insurance-Usecase\Policy-Document-Generation\Policy-Document-Generation\wwwroot\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blog\Insurance\Template change\Policy-Document-Generation\Policy-Document-Generation\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C43B51-3834-45B5-9AD8-B45763862C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A91436-FC1A-4703-87EC-74BA9898A130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PolicyDetails" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="110">
   <si>
     <t>PolicyNumber</t>
   </si>
@@ -216,9 +216,6 @@
     <t>Taylor</t>
   </si>
   <si>
-    <t>liam.taylor@company.au</t>
-  </si>
-  <si>
     <t>Civil Engineer</t>
   </si>
   <si>
@@ -342,12 +339,6 @@
     <t>HasADBS</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>emma.wilson@company.au</t>
-  </si>
-  <si>
     <t>12 Evergreen Terrace</t>
   </si>
   <si>
@@ -357,9 +348,6 @@
     <t>55 Harbour Road</t>
   </si>
   <si>
-    <t>michael.brown@company.au</t>
-  </si>
-  <si>
     <t>POL001</t>
   </si>
   <si>
@@ -367,13 +355,22 @@
   </si>
   <si>
     <t>POL003</t>
+  </si>
+  <si>
+    <t>415-555-9821</t>
+  </si>
+  <si>
+    <t>44-20-7946-958</t>
+  </si>
+  <si>
+    <t>61-2-9374-4000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,14 +383,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -428,11 +417,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -449,12 +437,8 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -755,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
@@ -763,15 +747,15 @@
     <col min="4" max="4" width="12.77734375" style="3" customWidth="1"/>
     <col min="5" max="7" width="17.44140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="18.21875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16" style="3" customWidth="1"/>
-    <col min="10" max="11" width="8.88671875" style="3"/>
-    <col min="12" max="12" width="19.21875" style="3" customWidth="1"/>
-    <col min="13" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="11.44140625" style="3" customWidth="1"/>
-    <col min="37" max="16384" width="8.88671875" style="3"/>
+    <col min="9" max="9" width="21" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="3"/>
+    <col min="11" max="11" width="19.21875" style="3" customWidth="1"/>
+    <col min="12" max="34" width="8.88671875" style="3"/>
+    <col min="35" max="35" width="11.44140625" style="3" customWidth="1"/>
+    <col min="36" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -791,99 +775,96 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="L1" s="2" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -901,100 +882,96 @@
         <v>33</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H2" s="5">
         <v>36842</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J2" s="3">
-        <f>1-415-555-9821</f>
-        <v>-10790</v>
+      <c r="J2" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="3">
+      <c r="N2" s="3">
         <v>94105</v>
       </c>
+      <c r="O2" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="P2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="S2" s="3">
+        <v>1000000</v>
+      </c>
       <c r="T2" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="U2" s="3">
         <v>1200</v>
       </c>
-      <c r="V2" s="3" t="b">
+      <c r="U2" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="V2" s="3">
+        <v>200000</v>
+      </c>
       <c r="W2" s="3">
-        <v>200000</v>
-      </c>
-      <c r="X2" s="3">
         <v>150</v>
       </c>
-      <c r="Y2" s="3" t="b">
+      <c r="X2" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="Y2" s="3">
+        <v>100000</v>
+      </c>
       <c r="Z2" s="3">
-        <v>100000</v>
-      </c>
-      <c r="AA2" s="3">
         <v>95</v>
       </c>
-      <c r="AB2" s="3" t="b">
+      <c r="AA2" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="AB2" s="3">
+        <v>100</v>
+      </c>
       <c r="AC2" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="AD2" s="3">
-        <v>30</v>
-      </c>
-      <c r="AE2" s="3">
         <v>120</v>
       </c>
-      <c r="AF2" s="3" t="b">
+      <c r="AE2" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="AF2" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AG2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AJ2" s="4">
+      <c r="AI2" s="4">
         <v>46037</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
@@ -1012,97 +989,93 @@
         <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H3" s="5">
         <v>37174</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="3">
-        <f>44-20-7946-958</f>
-        <v>-8880</v>
+      <c r="I3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="S3" s="3">
+        <v>750000</v>
+      </c>
       <c r="T3" s="3">
-        <v>750000</v>
-      </c>
-      <c r="U3" s="3">
         <v>980</v>
       </c>
-      <c r="V3" s="3" t="b">
+      <c r="U3" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="V3" s="3">
+        <v>150000</v>
+      </c>
       <c r="W3" s="3">
-        <v>150000</v>
-      </c>
-      <c r="X3" s="3">
         <v>110</v>
       </c>
-      <c r="Y3" s="3" t="b">
+      <c r="X3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3">
         <v>0</v>
       </c>
       <c r="Z3" s="3">
         <v>0</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>80</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>25</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>90</v>
+      </c>
+      <c r="AE3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AB3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>80</v>
-      </c>
-      <c r="AD3" s="3">
-        <v>25</v>
-      </c>
-      <c r="AE3" s="3">
-        <v>90</v>
-      </c>
-      <c r="AF3" s="3" t="b">
-        <v>0</v>
+      <c r="AG3" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AJ3" s="4">
+      <c r="AI3" s="4">
         <v>46101</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -1120,70 +1093,69 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="3">
-        <f>61-2-9374-4000</f>
-        <v>-13315</v>
-      </c>
       <c r="K4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="O4" s="3">
-        <v>2000</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="Q4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>66</v>
+      <c r="S4" s="3">
+        <v>600000</v>
       </c>
       <c r="T4" s="3">
-        <v>600000</v>
-      </c>
-      <c r="U4" s="3">
         <v>760</v>
       </c>
-      <c r="V4" s="3" t="b">
+      <c r="U4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
         <v>0</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>75000</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>70</v>
+      </c>
+      <c r="AA4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="Y4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>75000</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>70</v>
-      </c>
-      <c r="AB4" s="3" t="b">
+      <c r="AB4" s="3">
         <v>0</v>
       </c>
       <c r="AC4" s="3">
@@ -1192,11 +1164,11 @@
       <c r="AD4" s="3">
         <v>0</v>
       </c>
-      <c r="AE4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="3" t="b">
+      <c r="AE4" s="3" t="b">
         <v>1</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="AG4" s="3" t="s">
         <v>67</v>
@@ -1204,19 +1176,11 @@
       <c r="AH4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AI4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ4" s="4">
+      <c r="AI4" s="4">
         <v>46117</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" xr:uid="{143F9B3B-7FA2-40D2-815D-DC374F90869D}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{ACF89F23-8CCF-4B20-AA2B-56C89674C2A9}"/>
-    <hyperlink ref="I2" r:id="rId3" xr:uid="{62848935-DF13-4093-9A29-9C30B5464F69}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1236,102 +1200,102 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>76</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>78</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" t="s">
         <v>80</v>
       </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>81</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>82</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>83</v>
-      </c>
-      <c r="F3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
         <v>85</v>
       </c>
-      <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>86</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>87</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>88</v>
-      </c>
-      <c r="F4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>91</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>92</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>93</v>
-      </c>
-      <c r="F5" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
